--- a/out/Attention-mamba2_repeat_3_000005.xlsx
+++ b/out/Attention-mamba2_repeat_3_000005.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9470245394981234</v>
+        <v>2.499999930000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9470245394981234</v>
+        <v>2.499999930000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9470245394981234</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.3999999825000003</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.3999999825000003</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3470245394981235</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3470245394981235</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3470245394981235</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3470245394981235</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3470245394981235</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>3.329251253104851</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>3.329251253104851</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>3.329251253104851</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>3.329251253104851</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3470245394981235</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9470245394981234</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9470245394981234</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9470245394981234</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.729251253104851</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9470245394981234</v>
+        <v>2.499999930000001</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9470245394981234</v>
+        <v>2.499999930000001</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>3.329251253104851</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3470245394981235</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3470245394981235</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>3.329251253104851</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3470245394981235</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>3.329251253104851</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>3.329251253104851</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>3.329251253104851</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>3.329251253104851</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3470245394981235</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>2.729251253104851</v>
+        <v>2.499999930000001</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.729251253104851</v>
+        <v>2.499999930000001</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>3.329251253104851</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9470245394981234</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_3_000005.xlsx
+++ b/out/Attention-mamba2_repeat_3_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9470245394981234</v>
+        <v>0.5299763727307027</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>3.329251253104851</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3470245394981235</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>3.329251253104851</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>3.329251253104851</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3470245394981235</v>
+        <v>0.5299763727307026</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3470245394981235</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9470245394981234</v>
+        <v>0.3299763727307026</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>3.329251253104851</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>3.329251253104851</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>3.329251253104851</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3470245394981235</v>
+        <v>0.5299763727307026</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3470245394981235</v>
+        <v>-0.2958637449717586</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9470245394981234</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.329251253104851</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>3.329251253104851</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>3.329251253104851</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>3.329251253104851</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>3.329251253104851</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3470245394981235</v>
+        <v>0.5299763727307026</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9470245394981234</v>
+        <v>0.3299763727307026</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.729251253104851</v>
+        <v>0.3299763727307026</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9470245394981234</v>
+        <v>0.3299763727307026</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9470245394981234</v>
+        <v>0.3299763727307026</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.329251253104851</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>3.329251253104851</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3470245394981235</v>
+        <v>0.5299763727307026</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3470245394981235</v>
+        <v>-0.2958637449717586</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9470245394981234</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>3.329251253104851</v>
+        <v>0.5299763727307025</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3470245394981235</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>3.329251253104851</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>3.329251253104851</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>3.329251253104851</v>
+        <v>2.181656608135626</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>3.329251253104851</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3470245394981235</v>
+        <v>0.5299763727307026</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9470245394981234</v>
+        <v>0.3299763727307026</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>2.729251253104851</v>
+        <v>1.155816490433164</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.729251253104851</v>
+        <v>1.981656608135625</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>3.329251253104851</v>
+        <v>1.355816490433164</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9470245394981234</v>
+        <v>0.3299763727307026</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9470245394981234</v>
+        <v>-0.4958637449717587</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_3_000005.xlsx
+++ b/out/Attention-mamba2_repeat_3_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.1755597591400146</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4400000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.2135675102472305</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.37</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.1789065450429916</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.1966472417116165</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.2010240107774734</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.2053061276674271</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.2463881522417068</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.2077818661928177</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.2056196182966232</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.2165089398622513</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.2077533155679703</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.2062172442674637</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.1950644701719284</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.2090387493371964</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.2156825214624405</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.311327189207077</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.2873443067073822</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5299763727307027</v>
+        <v>0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.07069538533687592</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.355816490433164</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.08704370260238647</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.181656608135626</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.0356035977602005</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.181656608135626</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.02536318078637123</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.355816490433164</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.3259838819503784</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.5299763727307026</v>
+        <v>0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.2175555676221848</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.2850309312343597</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.208287701010704</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.2397521585226059</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.2872475385665894</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.2081846445798874</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.2287163585424423</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.2435307651758194</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.3299763727307026</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.04842612147331238</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.355816490433164</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.04623975604772568</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.181656608135626</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.09947872161865234</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.355816490433164</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.301512748003006</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5299763727307026</v>
+        <v>0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.2226980477571487</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.2958637449717586</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.3468419909477234</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.2314756363630295</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.2228063195943832</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.25483638048172</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.2539142668247223</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.2576939463615417</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.2029261440038681</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.2002016454935074</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.2326771467924118</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.2085935324430466</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.2157462984323502</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.2307443767786026</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.2113664299249649</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.2288492172956467</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.2151024788618088</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.2378702014684677</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.2194337099790573</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.2191577106714249</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.2543106079101562</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.2328448444604874</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.3730888664722443</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.2809333205223083</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.2897175550460815</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.276655912399292</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.2404417842626572</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.2773283123970032</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.16</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.2018443197011948</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.1995280534029007</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.1899294406175613</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.1892547756433487</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.212292954325676</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.2021615654230118</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.2017144709825516</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.2224429994821548</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.16</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.2174121290445328</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.16</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.1996862143278122</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.2261141091585159</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.5299763727307025</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.0952969491481781</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.355816490433164</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.09355373680591583</v>
       </c>
       <c r="JB75" t="n">
-        <v>2.181656608135626</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.04645159468054771</v>
       </c>
       <c r="JB76" t="n">
-        <v>2.181656608135626</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.05532668903470039</v>
       </c>
       <c r="JB77" t="n">
-        <v>2.181656608135626</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.1011797040700912</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.355816490433164</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.3654040396213531</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.5299763727307026</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.3448534607887268</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.3335377871990204</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.3553468286991119</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.3299763727307026</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.1570586413145065</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.3299763727307026</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.2985635995864868</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.3299763727307026</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.3646808862686157</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.3201117217540741</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.2532920837402344</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.3299763727307026</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.1132830381393433</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.355816490433164</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.1440500169992447</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.355816490433164</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.3792658746242523</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.5299763727307026</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.309406965970993</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2958637449717586</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.3299290239810944</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.3002067506313324</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.2819729447364807</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.3254916667938232</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.3665207624435425</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.3260148167610168</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.318187028169632</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.3158522844314575</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.2722961902618408</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.3172371685504913</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.3642380833625793</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.3242170214653015</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.3158723115921021</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.3585163950920105</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.3800681531429291</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.2876426577568054</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.3525150418281555</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.2859075963497162</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.2878365814685822</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.3</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.2364979833364487</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.2366776019334793</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4958637449717587</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.2228911966085434</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.5299763727307025</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.1247491240501404</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.5299763727307025</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.264103502035141</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.355816490433164</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.09185768663883209</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.355816490433164</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.08130017668008804</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.181656608135626</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.07517322152853012</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.181656608135626</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.1486928761005402</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.355816490433164</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.2447161823511124</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.5299763727307026</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.2249632328748703</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.3299763727307026</v>
+        <v>-0.16</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.08748406916856766</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.155816490433164</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.03235699236392975</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.981656608135625</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.05970467627048492</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.355816490433164</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.2917224168777466</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.3299763727307026</v>
+        <v>-0.7900000000000004</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.2284810692071915</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4958637449717587</v>
+        <v>-1.14</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_3_000005.xlsx
+++ b/out/Attention-mamba2_repeat_3_000005.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.1755597591400146</v>
+        <v>-0.1756897270679474</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.4400000000000001</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.2135675102472305</v>
+        <v>-0.2138449996709824</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.37</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.1789065450429916</v>
+        <v>-0.178823858499527</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.3</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.1966472417116165</v>
+        <v>-0.1982453018426895</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.4399999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.2010240107774734</v>
+        <v>-0.2003138810396194</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.4399999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.2053061276674271</v>
+        <v>-0.2045972496271133</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.7199999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.2463881522417068</v>
+        <v>-0.2457063347101212</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.8599999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.2077818661928177</v>
+        <v>-0.2073499411344528</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.2056196182966232</v>
+        <v>-0.2052772492170334</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.2165089398622513</v>
+        <v>-0.2162244468927383</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.2077533155679703</v>
+        <v>-0.2074366062879562</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.8599999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.2062172442674637</v>
+        <v>-0.2059106975793839</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.8599999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.1950644701719284</v>
+        <v>-0.195076510310173</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.8599999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.2090387493371964</v>
+        <v>-0.2089641839265823</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.8599999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.2156825214624405</v>
+        <v>-0.2155383378267288</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.2599999999999998</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.311327189207077</v>
+        <v>-0.3111682236194611</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.1199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.2873443067073822</v>
+        <v>-0.2866986691951752</v>
       </c>
       <c r="JB18" t="n">
         <v>0.16</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.07069538533687592</v>
+        <v>0.06964647769927979</v>
       </c>
       <c r="JB19" t="n">
         <v>0.4399999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.08704370260238647</v>
+        <v>0.08486917614936829</v>
       </c>
       <c r="JB20" t="n">
         <v>0.7199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.0356035977602005</v>
+        <v>0.03540139272809029</v>
       </c>
       <c r="JB21" t="n">
         <v>0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.02536318078637123</v>
+        <v>0.02502153255045414</v>
       </c>
       <c r="JB22" t="n">
         <v>0.4399999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.3259838819503784</v>
+        <v>-0.3257584571838379</v>
       </c>
       <c r="JB23" t="n">
         <v>0.16</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.2175555676221848</v>
+        <v>-0.2175414711236954</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.7199999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.2850309312343597</v>
+        <v>-0.2850053906440735</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.9999999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.208287701010704</v>
+        <v>-0.2079010754823685</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.9999999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.2397521585226059</v>
+        <v>-0.2394438832998276</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.9999999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.2872475385665894</v>
+        <v>-0.2871288359165192</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.9999999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.2081846445798874</v>
+        <v>-0.2079031020402908</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.2287163585424423</v>
+        <v>-0.2285154610872269</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.2435307651758194</v>
+        <v>-0.2430654913187027</v>
       </c>
       <c r="JB31" t="n">
         <v>0.16</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.04842612147331238</v>
+        <v>0.04863481596112251</v>
       </c>
       <c r="JB32" t="n">
         <v>0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.04623975604772568</v>
+        <v>0.04638032615184784</v>
       </c>
       <c r="JB33" t="n">
         <v>0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.09947872161865234</v>
+        <v>0.0997922420501709</v>
       </c>
       <c r="JB34" t="n">
         <v>0.4399999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.301512748003006</v>
+        <v>-0.3013795912265778</v>
       </c>
       <c r="JB35" t="n">
         <v>0.16</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.2226980477571487</v>
+        <v>-0.2223372906446457</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.1199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.3468419909477234</v>
+        <v>-0.3470191359519958</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.9999999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.2314756363630295</v>
+        <v>-0.231264129281044</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.2228063195943832</v>
+        <v>-0.222552701830864</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.9999999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.25483638048172</v>
+        <v>-0.2546824216842651</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.2539142668247223</v>
+        <v>-0.2537234723567963</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.2576939463615417</v>
+        <v>-0.2575637996196747</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.2029261440038681</v>
+        <v>-0.2026700526475906</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.2002016454935074</v>
+        <v>-0.1999160498380661</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.2326771467924118</v>
+        <v>-0.23275525867939</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.2085935324430466</v>
+        <v>-0.2083729654550552</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.2157462984323502</v>
+        <v>-0.2155743986368179</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.2307443767786026</v>
+        <v>-0.2307723611593246</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.2113664299249649</v>
+        <v>-0.2111353129148483</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.2288492172956467</v>
+        <v>-0.2288729399442673</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.2151024788618088</v>
+        <v>-0.2149132639169693</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.2378702014684677</v>
+        <v>-0.2380163818597794</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.2194337099790573</v>
+        <v>-0.219291940331459</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.2191577106714249</v>
+        <v>-0.2189758569002151</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.2543106079101562</v>
+        <v>-0.2546438872814178</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.2328448444604874</v>
+        <v>-0.232618972659111</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.3730888664722443</v>
+        <v>-0.3735293447971344</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.2809333205223083</v>
+        <v>-0.2813532650470734</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.2897175550460815</v>
+        <v>-0.2903513610363007</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.276655912399292</v>
+        <v>-0.2770529687404633</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.2404417842626572</v>
+        <v>-0.2403189688920975</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.1199999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.2773283123970032</v>
+        <v>-0.2780017554759979</v>
       </c>
       <c r="JB62" t="n">
         <v>0.16</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.2018443197011948</v>
+        <v>-0.2015199512243271</v>
       </c>
       <c r="JB63" t="n">
         <v>0.4399999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.1995280534029007</v>
+        <v>-0.1992589682340622</v>
       </c>
       <c r="JB64" t="n">
         <v>0.7199999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.1899294406175613</v>
+        <v>-0.1896067708730698</v>
       </c>
       <c r="JB65" t="n">
         <v>0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.1892547756433487</v>
+        <v>-0.188908115029335</v>
       </c>
       <c r="JB66" t="n">
         <v>0.8599999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.212292954325676</v>
+        <v>-0.2120131999254227</v>
       </c>
       <c r="JB67" t="n">
         <v>0.7199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.2021615654230118</v>
+        <v>-0.201847568154335</v>
       </c>
       <c r="JB68" t="n">
         <v>0.5799999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.2017144709825516</v>
+        <v>-0.2013853937387466</v>
       </c>
       <c r="JB69" t="n">
         <v>0.4399999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.2224429994821548</v>
+        <v>-0.2221706062555313</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.16</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.2174121290445328</v>
+        <v>-0.2171372622251511</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.16</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.1996862143278122</v>
+        <v>-0.1993498057126999</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.02000000000000007</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.2261141091585159</v>
+        <v>-0.2256321758031845</v>
       </c>
       <c r="JB73" t="n">
         <v>0.1199999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.0952969491481781</v>
+        <v>0.09578210860490799</v>
       </c>
       <c r="JB74" t="n">
         <v>0.8599999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.09355373680591583</v>
+        <v>0.09388595819473267</v>
       </c>
       <c r="JB75" t="n">
         <v>0.8599999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.04645159468054771</v>
+        <v>0.04680653288960457</v>
       </c>
       <c r="JB76" t="n">
         <v>0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.05532668903470039</v>
+        <v>0.05553402006626129</v>
       </c>
       <c r="JB77" t="n">
         <v>0.7199999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.1011797040700912</v>
+        <v>0.1014628261327744</v>
       </c>
       <c r="JB78" t="n">
         <v>0.4399999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.3654040396213531</v>
+        <v>-0.3652561902999878</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.4399999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.3448534607887268</v>
+        <v>-0.3447190821170807</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.7199999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.3335377871990204</v>
+        <v>-0.3333275318145752</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.7199999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.3553468286991119</v>
+        <v>-0.3549775183200836</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.7199999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.1570586413145065</v>
+        <v>0.1574261635541916</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.7199999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.2985635995864868</v>
+        <v>-0.2982854843139648</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.7199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.3646808862686157</v>
+        <v>-0.3646476864814758</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.7199999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.3201117217540741</v>
+        <v>-0.3200385868549347</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.8599999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.2532920837402344</v>
+        <v>-0.2527048587799072</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.5799999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.1132830381393433</v>
+        <v>0.1137910038232803</v>
       </c>
       <c r="JB88" t="n">
         <v>0.02000000000000007</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.1440500169992447</v>
+        <v>0.1443760097026825</v>
       </c>
       <c r="JB89" t="n">
         <v>0.02000000000000007</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.3792658746242523</v>
+        <v>-0.3792571723461151</v>
       </c>
       <c r="JB90" t="n">
         <v>0.02000000000000007</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.309406965970993</v>
+        <v>-0.3092055320739746</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.1199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.3299290239810944</v>
+        <v>-0.3298259675502777</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.9999999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.3002067506313324</v>
+        <v>-0.3000500202178955</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.2819729447364807</v>
+        <v>-0.2817202210426331</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.3254916667938232</v>
+        <v>-0.3252699375152588</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.3665207624435425</v>
+        <v>-0.366471141576767</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.3260148167610168</v>
+        <v>-0.3258740901947021</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.318187028169632</v>
+        <v>-0.3180294334888458</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.3158522844314575</v>
+        <v>-0.3157524466514587</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.2722961902618408</v>
+        <v>-0.2720300853252411</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.3172371685504913</v>
+        <v>-0.317006528377533</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.3642380833625793</v>
+        <v>-0.364193320274353</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.3242170214653015</v>
+        <v>-0.3240780532360077</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.3158723115921021</v>
+        <v>-0.315631777048111</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.3585163950920105</v>
+        <v>-0.358277827501297</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.3800681531429291</v>
+        <v>-0.3801494240760803</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.2876426577568054</v>
+        <v>-0.2873670160770416</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.2599999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.3525150418281555</v>
+        <v>-0.352519303560257</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.2599999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.2859075963497162</v>
+        <v>-0.2857226431369781</v>
       </c>
       <c r="JB109" t="n">
         <v>0.02000000000000007</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.2878365814685822</v>
+        <v>-0.2877047061920166</v>
       </c>
       <c r="JB110" t="n">
         <v>0.3</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.2364979833364487</v>
+        <v>-0.2362328618764877</v>
       </c>
       <c r="JB111" t="n">
         <v>0.5799999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.2366776019334793</v>
+        <v>-0.2364326864480972</v>
       </c>
       <c r="JB112" t="n">
         <v>0.7199999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.2228911966085434</v>
+        <v>-0.2224055081605911</v>
       </c>
       <c r="JB113" t="n">
         <v>0.8599999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.1247491240501404</v>
+        <v>0.1252465397119522</v>
       </c>
       <c r="JB114" t="n">
         <v>0.8599999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.264103502035141</v>
+        <v>-0.2634022831916809</v>
       </c>
       <c r="JB115" t="n">
         <v>0.8599999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.09185768663883209</v>
+        <v>0.0925915539264679</v>
       </c>
       <c r="JB116" t="n">
         <v>0.8599999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.08130017668008804</v>
+        <v>0.08172974735498428</v>
       </c>
       <c r="JB117" t="n">
         <v>0.8599999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.07517322152853012</v>
+        <v>0.07566377520561218</v>
       </c>
       <c r="JB118" t="n">
         <v>0.7199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.1486928761005402</v>
+        <v>0.1490809172391891</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.02000000000000007</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.2447161823511124</v>
+        <v>-0.2444989234209061</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.02000000000000007</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.2249632328748703</v>
+        <v>-0.2244619578123093</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.16</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.08748406916856766</v>
+        <v>0.08808821439743042</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.03235699236392975</v>
+        <v>0.03269597142934799</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.05970467627048492</v>
+        <v>0.05998335778713226</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.2917224168777466</v>
+        <v>-0.2916184663772583</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.7900000000000004</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.2284810692071915</v>
+        <v>-0.2281832545995712</v>
       </c>
       <c r="JB126" t="n">
         <v>-1.14</v>
